--- a/csv/model/FIC/formula_FIC_MB.xlsx
+++ b/csv/model/FIC/formula_FIC_MB.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X177"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>FIC</t>
+          <t>fic</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
